--- a/report_forms/031_crime_clearance_rate_report_form--report_forms.xlsx
+++ b/report_forms/031_crime_clearance_rate_report_form--report_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -711,8 +711,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="2" max="2"/>
+    <col width="27" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -740,12 +740,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'murder',_'value':_'murder'}</t>
+          <t>murder</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Murder', 'value': 'murder'}</t>
+          <t>Murder</t>
         </is>
       </c>
     </row>
@@ -757,12 +757,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'violent_crime',_'value':_'violent_crime'}</t>
+          <t>violent_crime</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Violent Crime', 'value': 'violent_crime'}</t>
+          <t>Violent Crime</t>
         </is>
       </c>
     </row>
@@ -774,12 +774,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'property_crime',_'value':_'property_crime'}</t>
+          <t>property_crime</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Property Crime', 'value': 'property_crime'}</t>
+          <t>Property Crime</t>
         </is>
       </c>
     </row>
@@ -791,12 +791,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'local_police_department',_'value':_'local_police_department'}</t>
+          <t>local_police_department</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Local Police Department', 'value': 'local_police_department'}</t>
+          <t>Local Police Department</t>
         </is>
       </c>
     </row>
@@ -808,12 +808,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'state_police_department',_'value':_'state_police_department'}</t>
+          <t>state_police_department</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'State Police Department', 'value': 'state_police_department'}</t>
+          <t>State Police Department</t>
         </is>
       </c>
     </row>
@@ -825,12 +825,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'federal_police_department',_'value':_'federal_police_department'}</t>
+          <t>federal_police_department</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Federal Police Department', 'value': 'federal_police_department'}</t>
+          <t>Federal Police Department</t>
         </is>
       </c>
     </row>
